--- a/data/daily/2026-09/2026-09-12.xlsx
+++ b/data/daily/2026-09/2026-09-12.xlsx
@@ -1170,14 +1170,39 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1217,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,160 +1267,110 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1425,207 +1425,207 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -2598,9 +2598,21 @@
       <c r="J2" t="n">
         <v>16031</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>피로 회복 효과 — 피곤함 완화 및 기력 회복에 도움이 됨</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>선물용 높은 만족도 — 생일이나 기력 회복 응원 선물로 적합함</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>체감되는 에너지 보충 — 섭취 후 기운이 나고 힘이 생김</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -2643,11 +2655,23 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15361</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+        <v>15366</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>피로 해소 및 개운함 — 면역력이 떨어지거나 무리한 날 복용 시 개운함</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>간편한 섭취 및 휴대성 — 작은 정제와 액상 형태로 물 없이 섭취가 용이함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>깔끔한 선물 패키지 — 쇼핑백과 깔끔한 포장이 함께 제공되어 선물용으로 좋음</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -2692,10 +2716,26 @@
       <c r="J4" t="n">
         <v>3345</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>피로 개선 효과 — 피로감이 줄어들고 몸이 건강해지는 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>뛰어난 맛과 섭취 편의성 — 맛이 상큼하고 한 병씩 챙겨 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>고급스러운 포장 디자인 — 고급 포장으로 생일이나 기념일 선물로 훌륭함</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>당뇨 환자 섭취 주의 — 당 성분이 포함되어 당뇨 질환자는 섭취 시 주의가 필요함</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -2737,11 +2777,23 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>8697</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>8698</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>간편한 올인원 섭취 — 여러 영양제를 따로 챙길 필요 없이 한 번에 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>피로 회복 체감 — 복용 후 체력이 회복되고 피로감이 덜함</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>알찬 선물 구성 — 추가 증정품이 포함되어 선물용으로 만족도가 높음</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -2786,10 +2838,26 @@
       <c r="J6" t="n">
         <v>6451</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>맛있고 쫄깃한 식감 — 새콤달콤한 과일 맛 젤리로 맛있게 섭취함</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>높은 복용 편의성 — 알약과 달리 젤리 형태라 잊지 않고 챙겨 먹게 됨</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>센스 있는 증정 굿즈 — 키캡 등 맘에 드는 굿즈가 동봉되어 선물하기 좋음</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>증정품 로고 표기 아쉬움 — 증정용 키캡 뒷면에 로고가 인쇄되어 있어 아쉬움</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -2833,9 +2901,21 @@
       <c r="J7" t="n">
         <v>731</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>뚜렷한 피로 회복 효과 — 지친 남편이나 가족의 컨디션 회복에 큰 도움이 됨</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>마시기 편한 액상 제형 — 하루 한 병 마시기 편하고 휴대성이 뛰어남</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>온 가족 건강 선물 — 선물용으로 인기가 높고 온 가족이 챙겨 먹기 좋음</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2880,9 +2960,21 @@
       <c r="J8" t="n">
         <v>777</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>한 번에 챙기는 편의성 — 귀찮은 영양제 섭취를 멀티비타민으로 한 번에 해결함</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>활력 충전 및 건강 증진 — 섭취 후 활력이 나고 건강해진 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>예쁜 선물 전용 포장 — 선물용 포장이 이쁘게 잘 되어 있어 선물용으로 적합함</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -2927,10 +3019,26 @@
       <c r="J9" t="n">
         <v>2612</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>빠른 피로 완화 — 피곤할 때 마시면 그날 피로감이 한결 줄어듦</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>맛있는 마시는 비타민 — 맛이 좋아 부담 없이 마시기 편함</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>고급스러운 선물 패키지 — 추석 및 응원 선물로 고급스러운 느낌을 줌</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>다소 적게 느껴지는 수량 — 용량이 적어 지속적인 섭취를 위해 많은 수량이 필요함</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -2972,11 +3080,23 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>1630</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+        <v>1631</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>원스탑 섭취 방식 — 액상에 분말을 눌러 섞어 한 번에 마시기 편함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>빠른 컨디션 회복 — 감기나 지친 일상에서 에너지 충전에 도움이 됨</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>알찬 추가 증정 구성 — 7입에 1입 추가 증정이 포함되어 구성이 알참</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -3021,9 +3141,21 @@
       <c r="J11" t="n">
         <v>768</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>피로 감소 효과 체감 — 꾸준히 복용 시 피로가 덜하고 컨디션 유지에 좋음</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>우수한 휴대성과 편의성 — 하루 한 개씩 챙기기 쉽고 휴대하기 용이함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>품격 있는 포장 디자인 — 포장에 성의가 느껴지고 선물받았을 때 기분이 좋음</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -3066,11 +3198,23 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>18</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>훌륭한 사은품 구성 — 포토카드와 엽서 등 굿즈 구성의 소장 가치가 높음</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>맛있는 베리말차 풍미 — 우유에 타서 딸기말차라떼 형태로 맛있게 즐김</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>장 운동 및 소화 지원 — 복용 후 속이 편안하고 장 운동에 도움을 줌</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -3115,9 +3259,21 @@
       <c r="J13" t="n">
         <v>732</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>고급스러운 오간자 포장 — 핑크빛 포장이 매우 고급스러워 선물 받는 느낌이 훌륭함</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>피부 맑아짐 체감 — 며칠간 복용 후 피부가 맑아지는 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>알찬 구성과 샘플 포함 — 본품 외 샘플 증정으로 만족스럽게 이용함</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -3162,10 +3318,26 @@
       <c r="J14" t="n">
         <v>50</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>부드럽고 다양한 맛 — 뻑뻑함이 덜하고 다양한 양념 맛으로 물리지 않음</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 패키지 — 저렴한 가격에 많은 닭가슴살 팩을 구매 가능함</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>간편한 전자레인지 조리 — 전자레인지 조리로 손쉽게 다이어트 식단을 챙김</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>배송 시 해동 발생 — 배송 과정에서 제품이 다소 녹아서 도착함</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
@@ -3209,9 +3381,21 @@
       <c r="J15" t="n">
         <v>213</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>비린 맛 없는 깔끔함 — 단백질 특유의 비린 맛이나 텁텁함 없이 달콤하고 맛있음</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>속 더부룩함 없는 편안함 — 목넘김이 부드럽고 마신 후 속이 더부룩하지 않음</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>낮은 당과 칼로리 — 당과 칼로리가 낮아 운동 후나 간식으로 부담 없음</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -3254,12 +3438,28 @@
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>142</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+        <v>143</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>다채로운 식단 구성 — 종류가 다양하여 매일 다른 맛으로 골라 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>유용한 보냉백 증정 — 증정되는 보냉 파우치 용량이 크고 도시락용으로 활용도 높음</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>풍부한 수량 대비 가성비 — 30팩 대용량을 합리적인 가격에 구매할 수 있음</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>배송 중 해동 우려 — 배송 시 일부 상품이 녹아서 올 수 있음</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
@@ -3303,9 +3503,21 @@
       <c r="J17" t="n">
         <v>1654</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>식후 속 편한 소화 지원 — 식사 후 더부룩함과 답답함을 완화해 줌</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>고소한 군고구마 맛 — 군고구마 풍미로 부담 없이 맛있게 섭취함</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>원활한 배변 활동 — 꾸준히 섭취 시 배변 활동에 유의미한 도움을 받음</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -3350,9 +3562,21 @@
       <c r="J18" t="n">
         <v>1900</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>근회복 및 운동 수행 지원 — 근회복에 도움을 주고 득근 및 에너지 유지에 효과적임</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>쉽고 간편한 섭취 — 물이나 음료에 섞어 부담 없이 매일 챙겨 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>귀여운 동봉 키링 — 증정되는 키링 굿즈가 귀엽고 만족스러움</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -3397,9 +3621,21 @@
       <c r="J19" t="n">
         <v>248</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>강력한 활력 증진 — 6,200mg 초고함량으로 피로 해소와 운동 수행력 향상에 도움됨</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>간편한 1포 개별 포장 — 1포씩 개별 포장되어 휴대와 섭취가 매우 편리함</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>고급스러운 패키지 구성 — 전용 쇼핑백과 추가 포 증정 구성으로 선물용에 적합함</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -3444,9 +3680,21 @@
       <c r="J20" t="n">
         <v>1534</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>깔끔한 정제 타입 — 알약 형태라 간편하게 복용할 수 있음</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>체감되는 피로 회복 — 아침에 일어날 때 몸이 한결 가볍고 하루 에너지가 도는 느낌임</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>넉넉한 2개월분 구성 — 용량이 넉넉하고 쇼핑백이 포함되어 활력 선물로 좋음</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3491,7 +3739,11 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>탁월한 숙취 해소 — 음주 전후 섭취 시 뛰어난 효과를 체감함</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3819,13 +4071,13 @@
         <v>16031</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15361</v>
+        <v>15366</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3345</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>8697</v>
+        <v>8698</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>6451</v>
@@ -3840,28 +4092,88 @@
         <v>2612</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>768</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>피로 회복 효과 — 피곤함 완화 및 기력 회복에 도움이 됨
+선물용 높은 만족도 — 생일이나 기력 회복 응원 선물로 적합함
+체감되는 에너지 보충 — 섭취 후 기운이 나고 힘이 생김</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>피로 해소 및 개운함 — 면역력이 떨어지거나 무리한 날 복용 시 개운함
+간편한 섭취 및 휴대성 — 작은 정제와 액상 형태로 물 없이 섭취가 용이함
+깔끔한 선물 패키지 — 쇼핑백과 깔끔한 포장이 함께 제공되어 선물용으로 좋음</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>피로 개선 효과 — 피로감이 줄어들고 몸이 건강해지는 느낌을 받음
+뛰어난 맛과 섭취 편의성 — 맛이 상큼하고 한 병씩 챙겨 먹기 편함
+고급스러운 포장 디자인 — 고급 포장으로 생일이나 기념일 선물로 훌륭함</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>간편한 올인원 섭취 — 여러 영양제를 따로 챙길 필요 없이 한 번에 섭취 가능함
+피로 회복 체감 — 복용 후 체력이 회복되고 피로감이 덜함
+알찬 선물 구성 — 추가 증정품이 포함되어 선물용으로 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>맛있고 쫄깃한 식감 — 새콤달콤한 과일 맛 젤리로 맛있게 섭취함
+높은 복용 편의성 — 알약과 달리 젤리 형태라 잊지 않고 챙겨 먹게 됨
+센스 있는 증정 굿즈 — 키캡 등 맘에 드는 굿즈가 동봉되어 선물하기 좋음</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>뚜렷한 피로 회복 효과 — 지친 남편이나 가족의 컨디션 회복에 큰 도움이 됨
+마시기 편한 액상 제형 — 하루 한 병 마시기 편하고 휴대성이 뛰어남
+온 가족 건강 선물 — 선물용으로 인기가 높고 온 가족이 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>한 번에 챙기는 편의성 — 귀찮은 영양제 섭취를 멀티비타민으로 한 번에 해결함
+활력 충전 및 건강 증진 — 섭취 후 활력이 나고 건강해진 느낌을 받음
+예쁜 선물 전용 포장 — 선물용 포장이 이쁘게 잘 되어 있어 선물용으로 적합함</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>빠른 피로 완화 — 피곤할 때 마시면 그날 피로감이 한결 줄어듦
+맛있는 마시는 비타민 — 맛이 좋아 부담 없이 마시기 편함
+고급스러운 선물 패키지 — 추석 및 응원 선물로 고급스러운 느낌을 줌</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>원스탑 섭취 방식 — 액상에 분말을 눌러 섞어 한 번에 마시기 편함
+빠른 컨디션 회복 — 감기나 지친 일상에서 에너지 충전에 도움이 됨
+알찬 추가 증정 구성 — 7입에 1입 추가 증정이 포함되어 구성이 알참</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>피로 감소 효과 체감 — 꾸준히 복용 시 피로가 덜하고 컨디션 유지에 좋음
+우수한 휴대성과 편의성 — 하루 한 개씩 챙기기 쉽고 휴대하기 용이함
+품격 있는 포장 디자인 — 포장에 성의가 느껴지고 선물받았을 때 기분이 좋음</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -3871,12 +4183,24 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>당뇨 환자 섭취 주의 — 당 성분이 포함되어 당뇨 질환자는 섭취 시 주의가 필요함</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>증정품 로고 표기 아쉬움 — 증정용 키캡 뒷면에 로고가 인쇄되어 있어 아쉬움</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>다소 적게 느껴지는 수량 — 용량이 적어 지속적인 섭취를 위해 많은 수량이 필요함</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
@@ -4283,7 +4607,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>732</v>
@@ -4295,7 +4619,7 @@
         <v>213</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>1654</v>
@@ -4313,22 +4637,80 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="90" customHeight="1">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>훌륭한 사은품 구성 — 포토카드와 엽서 등 굿즈 구성의 소장 가치가 높음
+맛있는 베리말차 풍미 — 우유에 타서 딸기말차라떼 형태로 맛있게 즐김
+장 운동 및 소화 지원 — 복용 후 속이 편안하고 장 운동에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>고급스러운 오간자 포장 — 핑크빛 포장이 매우 고급스러워 선물 받는 느낌이 훌륭함
+피부 맑아짐 체감 — 며칠간 복용 후 피부가 맑아지는 느낌을 받음
+알찬 구성과 샘플 포함 — 본품 외 샘플 증정으로 만족스럽게 이용함</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>부드럽고 다양한 맛 — 뻑뻑함이 덜하고 다양한 양념 맛으로 물리지 않음
+뛰어난 가성비 패키지 — 저렴한 가격에 많은 닭가슴살 팩을 구매 가능함
+간편한 전자레인지 조리 — 전자레인지 조리로 손쉽게 다이어트 식단을 챙김</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>비린 맛 없는 깔끔함 — 단백질 특유의 비린 맛이나 텁텁함 없이 달콤하고 맛있음
+속 더부룩함 없는 편안함 — 목넘김이 부드럽고 마신 후 속이 더부룩하지 않음
+낮은 당과 칼로리 — 당과 칼로리가 낮아 운동 후나 간식으로 부담 없음</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>다채로운 식단 구성 — 종류가 다양하여 매일 다른 맛으로 골라 먹기 좋음
+유용한 보냉백 증정 — 증정되는 보냉 파우치 용량이 크고 도시락용으로 활용도 높음
+풍부한 수량 대비 가성비 — 30팩 대용량을 합리적인 가격에 구매할 수 있음</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>식후 속 편한 소화 지원 — 식사 후 더부룩함과 답답함을 완화해 줌
+고소한 군고구마 맛 — 군고구마 풍미로 부담 없이 맛있게 섭취함
+원활한 배변 활동 — 꾸준히 섭취 시 배변 활동에 유의미한 도움을 받음</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>근회복 및 운동 수행 지원 — 근회복에 도움을 주고 득근 및 에너지 유지에 효과적임
+쉽고 간편한 섭취 — 물이나 음료에 섞어 부담 없이 매일 챙겨 먹기 편함
+귀여운 동봉 키링 — 증정되는 키링 굿즈가 귀엽고 만족스러움</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>강력한 활력 증진 — 6,200mg 초고함량으로 피로 해소와 운동 수행력 향상에 도움됨
+간편한 1포 개별 포장 — 1포씩 개별 포장되어 휴대와 섭취가 매우 편리함
+고급스러운 패키지 구성 — 전용 쇼핑백과 추가 포 증정 구성으로 선물용에 적합함</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>깔끔한 정제 타입 — 알약 형태라 간편하게 복용할 수 있음
+체감되는 피로 회복 — 아침에 일어날 때 몸이 한결 가볍고 하루 에너지가 도는 느낌임
+넉넉한 2개월분 구성 — 용량이 넉넉하고 쇼핑백이 포함되어 활력 선물로 좋음</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>탁월한 숙취 해소 — 음주 전후 섭취 시 뛰어난 효과를 체감함</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="1" t="inlineStr">
@@ -4338,9 +4720,17 @@
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>배송 시 해동 발생 — 배송 과정에서 제품이 다소 녹아서 도착함</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>배송 중 해동 우려 — 배송 시 일부 상품이 녹아서 올 수 있음</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
@@ -4590,7 +4980,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4598,12 +4988,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 다이어트 컷 올인원 15포 15일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4613,24 +5003,36 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991021&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/xVYROwLnuZYLoqWwcjU6033991021_00_00xVYROwLnuZYLoqWwcjU6.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>146</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+        <v>1915</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>부담 없는 저렴한 가격 — 타사 제품 대비 가성비가 매우 뛰어남</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>여성 건강 안정화 도움 — 꾸준히 복용 시 부정출혈 등의 안정화에 도움을 줌</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>아쉬운 맛과 풍미 — 양에 비해 맛이 별로여서 호불호가 갈릴 수 있음</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -4645,38 +5047,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>종근당 데일리와이즈 알로에 구미 7일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306211&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260414/Rr7eEkWvVmX4lCcRcfuW601618636_00_00Rr7eEkWvVmX4lCcRcfuW.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260417/a7p01ihsI7GPXC88B4Ec032306211_00_01a7p01ihsI7GPXC88B4Ec.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3263</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+        <v>205</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>말랑하고 쫄깃한 구미 — 구미 제형이라 쉽고 간편하게 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>상큼달콤한 과일 맛 — 달달하고 상큼한 사과 및 알로에 맛으로 맛있음</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>우수한 접근성과 가성비 — 다이소에서 저렴하고 쉽게 구매할 수 있음</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -4684,7 +5098,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4692,46 +5106,62 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4531</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>414</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>확실한 배변 활동 효과 — 섭취 후 변비 해소와 장 편안함에 효과가 뛰어남</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>압도적인 가성비 — 타 판매처 대비 훨씬 저렴한 가격에 구매 가능함</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>뛰어난 구매 접근성 — 필요할 때 매장에서 바로 살 수 있어 편리함</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>다소 강한 단맛 — 상큼하지만 단맛이 다소 강하게 느껴짐</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4739,38 +5169,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1192</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>5949</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>숙면 유도 및 수면 개선 — 취침 전 복용 시 잠을 훨씬 잘 자게 됨</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>약사 추천 가성비 — 약사 추천 제품으로 가격 부담이 적음</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>위생적인 포장 상태 — 깔끔한 포장으로 건강 관리에 좋음</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -4778,7 +5220,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4786,46 +5228,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
+          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953529&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=025575127&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/vXg1N5D0xbSNweDPvvl2994953529_00_00vXg1N5D0xbSNweDPvvl2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/VsX5iaJon2xHHTs8AQHv025575127_00_01VsX5iaJon2xHHTs8AQHv.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>320</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+        <v>837</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>다음 날 아침 붓기 완화 — 짠 음식을 먹은 뒤 복용하면 아침 붓기가 덜한 느낌을 줌</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>부담 없는 착한 가격 — 가성비가 좋아 부담 없이 붓기 관리를 시도하기 좋음</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>붓기 개선 효과 미미 — 사람에 따라 붓기 완화 효과를 체감하기 어려움</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4833,12 +5287,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4848,23 +5302,35 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651649&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/RN6BLb2wWdxkL0nu9aVK600651649_00_00RN6BLb2wWdxkL0nu9aVK.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>584</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+        <v>1501</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>삼키기 쉬운 작은 알약 — 알약 크기가 작아 목넘김이 편함</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>원활한 배변 활동 — 복용 후 화장실을 편하게 잘 가게 됨</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>휴대하기 편한 통 용기 — 통에 한 번에 들어있어 휴대하고 다니기 좋음</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -4872,7 +5338,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4880,12 +5346,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
+          <t>[보령약국 X Pantio] 다이어트 컷 올인원 15포 15일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>판티오</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4895,22 +5361,30 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306284&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991021&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/e483TrUWUwCko9CBv1Da032306284_00_00e483TrUWUwCko9CBv1Da.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260805/xVYROwLnuZYLoqWwcjU6033991021_00_00xVYROwLnuZYLoqWwcjU6.png</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>70</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+        <v>149</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>올인원 다이어트 성분 — 카테킨과 바나바잎 성분을 동시에 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>부담 없는 저렴한 가격 — 가성비 좋게 다이어트 관리가 가능함</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -4919,7 +5393,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4927,12 +5401,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4942,23 +5416,35 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000135&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031930043&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/2ijoJLmHVT94XXIOZnda600000135_00_002ijoJLmHVT94XXIOZnda.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260106/ifUNcDpBRic8ZZffJeay031930043_00_03ifUNcDpBRic8ZZffJeay.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3359</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+        <v>1602</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>확실한 수면 유도 — 자기 전 복용 시 졸음이 오며 꿀잠을 자는 데 도움을 줌</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>안심할 수 있는 성분 — 부작용 부담이 적어 안심하고 매일 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>가격 대비 뛰어난 효과 — 저렴한 가격에 수면 개선 효과가 우수함</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -4966,7 +5452,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4974,38 +5460,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306208&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260417/wEewWmXsoUl4j1ERyFu9032306208_00_01wEewWmXsoUl4j1ERyFu9.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>583</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+        <v>2819</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>고함량 비타민D 충족 — 약사 추천 고함량으로 햇빛 부족을 보완함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>생리 주기 정상화 체감 — 꾸준히 복용 시 생리불순 개선에 도움을 봄</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>매우 저렴한 대용량 — 용량이 넉넉하고 가격이 저렴해 매일 챙겨 먹기 좋음</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -5021,7 +5519,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5031,28 +5529,40 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>6119</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+        <v>3859</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>눈 피로 및 시야 개선 — 피로로 흐려지던 눈앞이 한결 개선되는 느낌임</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>부담 없는 30일 소용량 — 적은 수량으로 판매하여 섭취 후 재구매를 결정하기 좋음</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 약국보다 훨씬 저렴한 3천원 가격으로 루테인을 구매함</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -5168,47 +5678,47 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5225,47 +5735,47 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>종근당</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>판티오</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>동화약품</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>종근당</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5282,52 +5792,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>종근당 데일리와이즈 알로에 구미 7일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>[보령약국 X Pantio] 다이어트 컷 올인원 15포 15일분</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5854,7 @@
         <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.8</v>
@@ -5362,7 +5872,7 @@
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.8</v>
@@ -5375,52 +5885,109 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>146</v>
+        <v>1915</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3263</v>
+        <v>205</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>4531</v>
+        <v>414</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1192</v>
+        <v>5949</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>320</v>
+        <v>837</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>584</v>
+        <v>1501</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>3359</v>
+        <v>1602</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>583</v>
+        <v>2819</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>6119</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>3859</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>부담 없는 저렴한 가격 — 타사 제품 대비 가성비가 매우 뛰어남
+여성 건강 안정화 도움 — 꾸준히 복용 시 부정출혈 등의 안정화에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>말랑하고 쫄깃한 구미 — 구미 제형이라 쉽고 간편하게 먹을 수 있음
+상큼달콤한 과일 맛 — 달달하고 상큼한 사과 및 알로에 맛으로 맛있음
+우수한 접근성과 가성비 — 다이소에서 저렴하고 쉽게 구매할 수 있음</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>확실한 배변 활동 효과 — 섭취 후 변비 해소와 장 편안함에 효과가 뛰어남
+압도적인 가성비 — 타 판매처 대비 훨씬 저렴한 가격에 구매 가능함
+뛰어난 구매 접근성 — 필요할 때 매장에서 바로 살 수 있어 편리함</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>숙면 유도 및 수면 개선 — 취침 전 복용 시 잠을 훨씬 잘 자게 됨
+약사 추천 가성비 — 약사 추천 제품으로 가격 부담이 적음
+위생적인 포장 상태 — 깔끔한 포장으로 건강 관리에 좋음</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>다음 날 아침 붓기 완화 — 짠 음식을 먹은 뒤 복용하면 아침 붓기가 덜한 느낌을 줌
+부담 없는 착한 가격 — 가성비가 좋아 부담 없이 붓기 관리를 시도하기 좋음</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>삼키기 쉬운 작은 알약 — 알약 크기가 작아 목넘김이 편함
+원활한 배변 활동 — 복용 후 화장실을 편하게 잘 가게 됨
+휴대하기 편한 통 용기 — 통에 한 번에 들어있어 휴대하고 다니기 좋음</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>올인원 다이어트 성분 — 카테킨과 바나바잎 성분을 동시에 챙길 수 있음
+부담 없는 저렴한 가격 — 가성비 좋게 다이어트 관리가 가능함</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>확실한 수면 유도 — 자기 전 복용 시 졸음이 오며 꿀잠을 자는 데 도움을 줌
+안심할 수 있는 성분 — 부작용 부담이 적어 안심하고 매일 먹을 수 있음
+가격 대비 뛰어난 효과 — 저렴한 가격에 수면 개선 효과가 우수함</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>고함량 비타민D 충족 — 약사 추천 고함량으로 햇빛 부족을 보완함
+생리 주기 정상화 체감 — 꾸준히 복용 시 생리불순 개선에 도움을 봄
+매우 저렴한 대용량 — 용량이 넉넉하고 가격이 저렴해 매일 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>눈 피로 및 시야 개선 — 피로로 흐려지던 눈앞이 한결 개선되는 느낌임
+부담 없는 30일 소용량 — 적은 수량으로 판매하여 섭취 후 재구매를 결정하기 좋음
+뛰어난 가성비 — 약국보다 훨씬 저렴한 3천원 가격으로 루테인을 구매함</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -5428,11 +5995,23 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 맛과 풍미 — 양에 비해 맛이 별로여서 호불호가 갈릴 수 있음</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>다소 강한 단맛 — 상큼하지만 단맛이 다소 강하게 느껴짐</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>붓기 개선 효과 미미 — 사람에 따라 붓기 완화 효과를 체감하기 어려움</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
@@ -5452,47 +6031,47 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -5706,7 +6285,7 @@
         <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>9931</v>
+        <v>9935</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -5718,7 +6297,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5726,38 +6305,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12,500원</t>
+          <t>15,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014346ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>12388</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+        <v>14868</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>빠르고 깊은 숙면 효과 — 자기 전 복용 시 빠르게 깊은 잠에 들게 됨</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>맛있고 간편한 젤리 제형 — 새콤달콤 구미 타입이라 부담 없이 챙겨 먹음</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>식물성 성분의 안심 섭취 — 식물성 멜라토닌 성분이라 안심하고 섭취함</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -5765,7 +6356,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5773,38 +6364,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>12,500원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014346ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>14864</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+        <v>12392</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>속 편한 장 건강 케어 — 100억 보장 균수로 배 아픔이나 가스 없이 화장실을 감</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>피부 면역 겸용 케어 — 장 건강뿐만 아니라 피부 면역 향상에도 도움을 줌</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>귀여운 산리오 굿즈 — 러기지택 등 기획 구성품이 매우 귀여움</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -5812,7 +6415,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5820,34 +6423,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15407</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>비타민 C+D 맞춤 조합 — 트러블 유발 가능성이 있는 비타민B 없이 C와 D만 알차게 챙김</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>피로 및 면역력 관리 — 실내 생활 부족분 보완과 피로 회복에 도움됨</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>높은 가성비와 신뢰도 — 대한민국 1등 비타민 브랜드로 믿고 먹음</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -5855,7 +6474,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5863,38 +6482,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>41035</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+        <v>8104</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>질과 장 복합 케어 — 질 건강과 장 건강을 한 번에 케어할 수 있음</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>알찬 더블 기획 구성 — 60캡슐 2개월분 구성으로 오래 복용하기 좋음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>공유 포토카드 굿즈 — 증정되는 포토카드 구성품에 만족도가 높음</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -5902,7 +6533,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5910,38 +6541,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>오쏘몰 바이탈 M/F 멀티비타민&amp;미네랄 30일분 (M:남성,F:여성)</t>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>99,000원</t>
+          <t>9,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000198827&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000187268&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019882703ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018726811ko.png?l=ko</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>4959</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+        <v>5616</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>고용량 비타민C 성분 — 고용량 메가도스로 피로 해소 효과가 뛰어남</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>흡수 빠른 가루 타입 — 가루 제형으로 피로할 때 빠르게 컨디션을 올림</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>소장 가치 높은 굿즈 — 헬로키티 파우치 증정으로 만족스러움</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -5949,7 +6592,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5957,38 +6600,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>53,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>20010</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+        <v>41038</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>강력한 활력 풀충전 — 지치고 피곤할 때 먹으면 활력이 도는 느낌임</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>간편한 올인원 액상형 — 하루 한 병으로 간편하게 비타민과 미네랄을 챙김</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>귀여운 포켓몬 굿즈 — 피카츄 등 증정 굿즈 퀄리티가 훌륭함</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -5996,7 +6651,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6004,38 +6659,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236755&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023675540ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>5938</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+        <v>465</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>체지방과 장 동시 관리 — 장 케어와 체지방 감량을 동시에 돕는 이중 기능성임</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>상큼한 요거트 맛 — 맛있는 요거트 풍미로 매일 한 포씩 챙기기 편함</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>인증된 효과와 높은 신뢰 — 식약처 인증 및 선수·연예인 복용으로 신뢰함</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -6043,7 +6710,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6051,38 +6718,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 다이어트 유산균 14캡슐 (+1캡슐) (+산리오 러기지택)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15,500원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000259858&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025985808ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>712</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+        <v>25042</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>170mg 초소형 캡슐 — 알약 크기가 매우 작고 가벼워 목넘김이 훌륭함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>질과 장 더블 케어 — 보장균수 50억으로 질과 장 건강을 한 번에 챙김</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>실용적인 포켓몬 굿즈 — 카드케이스 등 증정 굿즈 활용도가 좋음</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -6098,38 +6777,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[화사 PICK] CJ 바이오코어 피부면역유산균 30포 (+10포 증정기획) (20일분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12,500원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237417&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023741712ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>11824</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+        <v>24200</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>세계 1등 유산균 원료 — 검증된 원료로 장 건강과 면역력을 확실히 케어함</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>작은 캡슐의 편리함 — 사이즈가 작아 아침 공복에 마시기 수월함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>알찬 1+1 기획 세트 — 1+1에 추가 비타민까지 구성되어 가성비가 훌륭함</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -6250,42 +6941,42 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -6307,47 +6998,47 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>바이오코어유산균</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>지노마스터</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>빌드</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>코자아</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>덴프스</t>
         </is>
       </c>
     </row>
@@ -6364,47 +7055,47 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰 바이탈 M/F 멀티비타민&amp;미네랄 30일분 (M:남성,F:여성)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 다이어트 유산균 14캡슐 (+1캡슐) (+산리오 러기지택)</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[화사 PICK] CJ 바이오코어 피부면역유산균 30포 (+10포 증정기획) (20일분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
     </row>
@@ -6423,7 +7114,9 @@
       <c r="E6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="n">
+        <v>4.9</v>
+      </c>
       <c r="G6" s="3" t="n">
         <v>4.9</v>
       </c>
@@ -6431,16 +7124,16 @@
         <v>4.9</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -6450,50 +7143,106 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>9931</v>
+        <v>9935</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>12388</v>
+        <v>14868</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>14864</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>12392</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>15407</v>
+      </c>
       <c r="G7" s="3" t="n">
-        <v>41035</v>
+        <v>8104</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>4959</v>
+        <v>5616</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>20010</v>
+        <v>41038</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>5938</v>
+        <v>465</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>712</v>
+        <v>25042</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>11824</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>24200</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>빠르고 깊은 숙면 효과 — 자기 전 복용 시 빠르게 깊은 잠에 들게 됨
+맛있고 간편한 젤리 제형 — 새콤달콤 구미 타입이라 부담 없이 챙겨 먹음
+식물성 성분의 안심 섭취 — 식물성 멜라토닌 성분이라 안심하고 섭취함</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>속 편한 장 건강 케어 — 100억 보장 균수로 배 아픔이나 가스 없이 화장실을 감
+피부 면역 겸용 케어 — 장 건강뿐만 아니라 피부 면역 향상에도 도움을 줌
+귀여운 산리오 굿즈 — 러기지택 등 기획 구성품이 매우 귀여움</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>비타민 C+D 맞춤 조합 — 트러블 유발 가능성이 있는 비타민B 없이 C와 D만 알차게 챙김
+피로 및 면역력 관리 — 실내 생활 부족분 보완과 피로 회복에 도움됨
+높은 가성비와 신뢰도 — 대한민국 1등 비타민 브랜드로 믿고 먹음</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>질과 장 복합 케어 — 질 건강과 장 건강을 한 번에 케어할 수 있음
+알찬 더블 기획 구성 — 60캡슐 2개월분 구성으로 오래 복용하기 좋음
+공유 포토카드 굿즈 — 증정되는 포토카드 구성품에 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>고용량 비타민C 성분 — 고용량 메가도스로 피로 해소 효과가 뛰어남
+흡수 빠른 가루 타입 — 가루 제형으로 피로할 때 빠르게 컨디션을 올림
+소장 가치 높은 굿즈 — 헬로키티 파우치 증정으로 만족스러움</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>강력한 활력 풀충전 — 지치고 피곤할 때 먹으면 활력이 도는 느낌임
+간편한 올인원 액상형 — 하루 한 병으로 간편하게 비타민과 미네랄을 챙김
+귀여운 포켓몬 굿즈 — 피카츄 등 증정 굿즈 퀄리티가 훌륭함</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>체지방과 장 동시 관리 — 장 케어와 체지방 감량을 동시에 돕는 이중 기능성임
+상큼한 요거트 맛 — 맛있는 요거트 풍미로 매일 한 포씩 챙기기 편함
+인증된 효과와 높은 신뢰 — 식약처 인증 및 선수·연예인 복용으로 신뢰함</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>170mg 초소형 캡슐 — 알약 크기가 매우 작고 가벼워 목넘김이 훌륭함
+질과 장 더블 케어 — 보장균수 50억으로 질과 장 건강을 한 번에 챙김
+실용적인 포켓몬 굿즈 — 카드케이스 등 증정 굿즈 활용도가 좋음</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>세계 1등 유산균 원료 — 검증된 원료로 장 건강과 면역력을 확실히 케어함
+작은 캡슐의 편리함 — 사이즈가 작아 아침 공복에 마시기 수월함
+알찬 1+1 기획 세트 — 1+1에 추가 비타민까지 구성되어 가성비가 훌륭함</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -6525,47 +7274,47 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>15,900원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>12,500원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>15,900원</t>
-        </is>
-      </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>31,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>53,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>39,800원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>27,400원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>53,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>99,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>18,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>32,900원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>15,500원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>12,500원</t>
+          <t>30,400원</t>
         </is>
       </c>
     </row>
@@ -6653,7 +7402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6691,39 +7440,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>27.5</v>
+        <v>22.5</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -6735,23 +7484,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>27.5</v>
+        <v>22.5</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -6761,47 +7510,47 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6811,10 +7560,10 @@
         <v>2.5</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -6823,7 +7572,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6833,19 +7582,19 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6855,12 +7604,56 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
